--- a/artfynd/A 52345-2024 artfynd.xlsx
+++ b/artfynd/A 52345-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128862503</v>
       </c>
       <c r="B2" t="n">
-        <v>92294</v>
+        <v>92299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128862509</v>
       </c>
       <c r="B3" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128862506</v>
       </c>
       <c r="B4" t="n">
-        <v>88894</v>
+        <v>88899</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 52345-2024 artfynd.xlsx
+++ b/artfynd/A 52345-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128862503</v>
       </c>
       <c r="B2" t="n">
-        <v>92299</v>
+        <v>92304</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128862509</v>
       </c>
       <c r="B3" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128862506</v>
       </c>
       <c r="B4" t="n">
-        <v>88899</v>
+        <v>88904</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 52345-2024 artfynd.xlsx
+++ b/artfynd/A 52345-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128862503</v>
       </c>
       <c r="B2" t="n">
-        <v>92304</v>
+        <v>92308</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128862509</v>
       </c>
       <c r="B3" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128862506</v>
       </c>
       <c r="B4" t="n">
-        <v>88904</v>
+        <v>88908</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 52345-2024 artfynd.xlsx
+++ b/artfynd/A 52345-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128862503</v>
       </c>
       <c r="B2" t="n">
-        <v>92308</v>
+        <v>92313</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128862509</v>
       </c>
       <c r="B3" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128862506</v>
       </c>
       <c r="B4" t="n">
-        <v>88908</v>
+        <v>88913</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 52345-2024 artfynd.xlsx
+++ b/artfynd/A 52345-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128862503</v>
       </c>
       <c r="B2" t="n">
-        <v>92321</v>
+        <v>92326</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128862509</v>
       </c>
       <c r="B3" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128862506</v>
       </c>
       <c r="B4" t="n">
-        <v>88920</v>
+        <v>88923</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 52345-2024 artfynd.xlsx
+++ b/artfynd/A 52345-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128862503</v>
       </c>
       <c r="B2" t="n">
-        <v>92326</v>
+        <v>92329</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128862509</v>
       </c>
       <c r="B3" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128862506</v>
       </c>
       <c r="B4" t="n">
-        <v>88923</v>
+        <v>88926</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 52345-2024 artfynd.xlsx
+++ b/artfynd/A 52345-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128862503</v>
       </c>
       <c r="B2" t="n">
-        <v>92329</v>
+        <v>92336</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128862509</v>
       </c>
       <c r="B3" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128862506</v>
       </c>
       <c r="B4" t="n">
-        <v>88926</v>
+        <v>88930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 52345-2024 artfynd.xlsx
+++ b/artfynd/A 52345-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128862503</v>
       </c>
       <c r="B2" t="n">
-        <v>92336</v>
+        <v>92343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128862509</v>
       </c>
       <c r="B3" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128862506</v>
       </c>
       <c r="B4" t="n">
-        <v>88930</v>
+        <v>88937</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 52345-2024 artfynd.xlsx
+++ b/artfynd/A 52345-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128862503</v>
       </c>
       <c r="B2" t="n">
-        <v>92343</v>
+        <v>92345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128862509</v>
       </c>
       <c r="B3" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128862506</v>
       </c>
       <c r="B4" t="n">
-        <v>88937</v>
+        <v>88939</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 52345-2024 artfynd.xlsx
+++ b/artfynd/A 52345-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128862503</v>
       </c>
       <c r="B2" t="n">
-        <v>92345</v>
+        <v>92359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128862509</v>
       </c>
       <c r="B3" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128862506</v>
       </c>
       <c r="B4" t="n">
-        <v>88939</v>
+        <v>88940</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 52345-2024 artfynd.xlsx
+++ b/artfynd/A 52345-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128862503</v>
       </c>
       <c r="B2" t="n">
-        <v>92359</v>
+        <v>92360</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128862509</v>
       </c>
       <c r="B3" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52345-2024 artfynd.xlsx
+++ b/artfynd/A 52345-2024 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128862509</v>
       </c>
       <c r="B3" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52345-2024 artfynd.xlsx
+++ b/artfynd/A 52345-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128862503</v>
       </c>
       <c r="B2" t="n">
-        <v>92360</v>
+        <v>92363</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128862509</v>
       </c>
       <c r="B3" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128862506</v>
       </c>
       <c r="B4" t="n">
-        <v>88940</v>
+        <v>88943</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 52345-2024 artfynd.xlsx
+++ b/artfynd/A 52345-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128862503</v>
+        <v>128862506</v>
       </c>
       <c r="B2" t="n">
-        <v>92363</v>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2014</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533833</v>
+        <v>533739</v>
       </c>
       <c r="R2" t="n">
-        <v>7036363</v>
+        <v>7036268</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128862509</v>
+        <v>128862503</v>
       </c>
       <c r="B3" t="n">
-        <v>100899</v>
+        <v>92732</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>2014</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533761</v>
+        <v>533833</v>
       </c>
       <c r="R3" t="n">
-        <v>7036254</v>
+        <v>7036363</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128862506</v>
+        <v>88694117</v>
       </c>
       <c r="B4" t="n">
-        <v>88943</v>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,34 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stor-laxsjön N, Jmt</t>
+          <t>Mörttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533739</v>
+        <v>533984</v>
       </c>
       <c r="R4" t="n">
-        <v>7036268</v>
+        <v>7036254</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -934,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2020-09-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2020-09-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -950,19 +950,124 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Magnus Johansson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Johansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128862509</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stor-laxsjön N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>533761</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7036254</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Borgvattnet</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Benny Öwre</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Benny Öwre</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52345-2024 artfynd.xlsx
+++ b/artfynd/A 52345-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128862506</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128862503</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,6 +986,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88694117</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1068,8 +1088,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128862509</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>